--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-20_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-20_nm_basis-False_nm_modifier-False.xlsx
@@ -10,6 +10,7 @@
     <sheet name="nrr_8" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="summary_t" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrr_4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1140,44 @@
         <v>4.937501033558354</v>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>58.35940622323722</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57.51526703848037</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9585012481858332</v>
+      </c>
+      <c r="D4" t="n">
+        <v>58.35940622323722</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7.703872558557478</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8.075939047173611</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1659044645695794</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.703872558557479</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1155,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1265,681 @@
         <v>0.1330551446362266</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>58.35940622323722</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7.703872558557478</v>
+      </c>
+      <c r="C3" t="n">
+        <v>57.51526703848037</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.075939047173611</v>
+      </c>
+      <c r="E3" t="n">
+        <v>58.35940622323722</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.703872558557479</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9585012481858332</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1659044645695794</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>56.85896936824713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>55.88723157196254</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.001057260235151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>56.85896936824713</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60.36652566198669</v>
+      </c>
+      <c r="C3" t="n">
+        <v>59.9464247800659</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9067463050285974</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60.36652566198669</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.2700369380358</v>
+      </c>
+      <c r="C4" t="n">
+        <v>55.05890465156993</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.066935821374257</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.2700369380358</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50.69325859220235</v>
+      </c>
+      <c r="C5" t="n">
+        <v>49.61263784718345</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.119044375419617</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.69325859220235</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>51.67380340660386</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50.66755580965174</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.066651487847169</v>
+      </c>
+      <c r="E6" t="n">
+        <v>51.67380340660386</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>53.96742186351092</v>
+      </c>
+      <c r="C7" t="n">
+        <v>53.57577032047216</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9802178541819255</v>
+      </c>
+      <c r="E7" t="n">
+        <v>53.96742186351094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>67.08596095121929</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65.31993866626067</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7018803760409356</v>
+      </c>
+      <c r="E8" t="n">
+        <v>67.08596095121931</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62.19370409778632</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61.39646776393811</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9106962939103445</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62.1937040977863</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>67.28916340106748</v>
+      </c>
+      <c r="C10" t="n">
+        <v>67.31537434021583</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7619886785745621</v>
+      </c>
+      <c r="E10" t="n">
+        <v>67.28916340106748</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>51.52060138928537</v>
+      </c>
+      <c r="C11" t="n">
+        <v>49.54668439678547</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.181443334619204</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.52060138928537</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>53.58013477625239</v>
+      </c>
+      <c r="C12" t="n">
+        <v>52.6091764092027</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.022422597805659</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53.58013477625239</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>59.01841711433489</v>
+      </c>
+      <c r="C13" t="n">
+        <v>57.98082961845893</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9817920873562495</v>
+      </c>
+      <c r="E13" t="n">
+        <v>59.01841711433489</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>48.75396845993478</v>
+      </c>
+      <c r="C14" t="n">
+        <v>45.81210923668591</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.17477440237999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>48.75396845993477</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>52.37657765205581</v>
+      </c>
+      <c r="C15" t="n">
+        <v>51.72121851085581</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.091950052976608</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52.37657765205581</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>52.99933390427253</v>
+      </c>
+      <c r="C16" t="n">
+        <v>52.45086909025953</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.044454775253932</v>
+      </c>
+      <c r="E16" t="n">
+        <v>52.99933390427253</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>59.01339976989421</v>
+      </c>
+      <c r="C17" t="n">
+        <v>58.24422276182298</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9880358378092449</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.01339976989421</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>58.57230598880614</v>
+      </c>
+      <c r="C18" t="n">
+        <v>58.22468423374274</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.884431896607081</v>
+      </c>
+      <c r="E18" t="n">
+        <v>58.57230598880614</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>62.59232346300573</v>
+      </c>
+      <c r="C19" t="n">
+        <v>61.65772527978847</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9017964869737625</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62.59232346300573</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>57.56053253055823</v>
+      </c>
+      <c r="C20" t="n">
+        <v>57.25492404955131</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9426112363735836</v>
+      </c>
+      <c r="E20" t="n">
+        <v>57.56053253055823</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>53.8853277277485</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53.31413930569713</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.039090329408646</v>
+      </c>
+      <c r="E21" t="n">
+        <v>53.8853277277485</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>60.91955812766546</v>
+      </c>
+      <c r="C22" t="n">
+        <v>60.63449499287392</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9207515637079874</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60.91955812766546</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53.96517270910648</v>
+      </c>
+      <c r="C23" t="n">
+        <v>52.91254123643544</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.057324808835983</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53.96517270910648</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>49.6699798441163</v>
+      </c>
+      <c r="C24" t="n">
+        <v>48.15587565503739</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.156035377581914</v>
+      </c>
+      <c r="E24" t="n">
+        <v>49.6699798441163</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>52.78402062301577</v>
+      </c>
+      <c r="C25" t="n">
+        <v>52.07510225751163</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.080966683228811</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52.78402062301577</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63.22649849912197</v>
+      </c>
+      <c r="C26" t="n">
+        <v>62.67725820754197</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8659929811954499</v>
+      </c>
+      <c r="E26" t="n">
+        <v>63.22649849912197</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>51.32258929575515</v>
+      </c>
+      <c r="C27" t="n">
+        <v>49.649838822647</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.09331523279349</v>
+      </c>
+      <c r="E27" t="n">
+        <v>51.32258929575515</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>55.44096402218013</v>
+      </c>
+      <c r="C28" t="n">
+        <v>54.82063869978131</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9793348242839178</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55.44096402218013</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>73.95271585394337</v>
+      </c>
+      <c r="C29" t="n">
+        <v>74.13293639682098</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.646812637646993</v>
+      </c>
+      <c r="E29" t="n">
+        <v>73.95271585394337</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>70.0269898528534</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69.62321544711598</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7746293634176254</v>
+      </c>
+      <c r="E30" t="n">
+        <v>70.0269898528534</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>83.20193081255027</v>
+      </c>
+      <c r="C31" t="n">
+        <v>83.17922079447393</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4118524827063084</v>
+      </c>
+      <c r="E31" t="n">
+        <v>83.20193081255027</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>58.35940622323722</v>
+      </c>
+      <c r="C32" t="n">
+        <v>57.51526703848037</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9585012481858332</v>
+      </c>
+      <c r="E32" t="n">
+        <v>58.35940622323722</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7.703872558557478</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.075939047173611</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1659044645695794</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.703872558557479</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
